--- a/Datos 03.01 - I.xlsx
+++ b/Datos 03.01 - I.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jmedina\ParaCrucesCovid\SalaVirtual\INSUMOS_transferencia\Archivos Sala situacional\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Cursos\Introduccion a la Ciencia de Datos\GitHub\EP1053\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{159C3356-64DC-46CD-8F59-99A4BE9EE5B2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E210B403-E580-495B-BE50-432FEAAA5886}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="300" windowWidth="28800" windowHeight="15300"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CASOS_10082020" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
   <si>
     <t>Pais</t>
   </si>
@@ -119,12 +119,15 @@
   </si>
   <si>
     <t>LIMA REGIÓN</t>
+  </si>
+  <si>
+    <t>PRUEBA ANTIGENO(+)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -958,11 +961,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -976,13 +979,16 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -990,19 +996,22 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>78277</v>
+        <v>206585</v>
       </c>
       <c r="D2">
-        <v>146559</v>
+        <v>277989</v>
       </c>
       <c r="E2">
-        <v>224836</v>
+        <v>17177</v>
       </c>
       <c r="F2">
-        <v>9040</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>501751</v>
+      </c>
+      <c r="G2">
+        <v>16862</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1010,19 +1019,22 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>5891</v>
+        <v>15499</v>
       </c>
       <c r="D3">
-        <v>17199</v>
+        <v>33696</v>
       </c>
       <c r="E3">
-        <v>23090</v>
+        <v>1865</v>
       </c>
       <c r="F3">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>51060</v>
+      </c>
+      <c r="G3">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1030,19 +1042,22 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>2860</v>
+        <v>6750</v>
       </c>
       <c r="D4">
-        <v>14809</v>
+        <v>33798</v>
       </c>
       <c r="E4">
-        <v>17669</v>
+        <v>826</v>
       </c>
       <c r="F4">
-        <v>1432</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>41374</v>
+      </c>
+      <c r="G4">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1050,19 +1065,22 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>3667</v>
+        <v>10987</v>
       </c>
       <c r="D5">
-        <v>16216</v>
+        <v>43235</v>
       </c>
       <c r="E5">
-        <v>19883</v>
+        <v>1395</v>
       </c>
       <c r="F5">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>55617</v>
+      </c>
+      <c r="G5">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1070,19 +1088,22 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>307</v>
+        <v>1524</v>
       </c>
       <c r="D6">
-        <v>4438</v>
+        <v>16655</v>
       </c>
       <c r="E6">
-        <v>4745</v>
+        <v>380</v>
       </c>
       <c r="F6">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>18559</v>
+      </c>
+      <c r="G6">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1090,19 +1111,22 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>3050</v>
+        <v>8936</v>
       </c>
       <c r="D7">
-        <v>3829</v>
+        <v>20401</v>
       </c>
       <c r="E7">
-        <v>6879</v>
+        <v>1237</v>
       </c>
       <c r="F7">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30574</v>
+      </c>
+      <c r="G7">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1110,19 +1134,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>2108</v>
+        <v>6334</v>
       </c>
       <c r="D8">
-        <v>16767</v>
+        <v>29782</v>
       </c>
       <c r="E8">
-        <v>18875</v>
+        <v>312</v>
       </c>
       <c r="F8">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>36428</v>
+      </c>
+      <c r="G8">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1130,19 +1157,22 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>950</v>
+        <v>3629</v>
       </c>
       <c r="D9">
-        <v>21786</v>
+        <v>42337</v>
       </c>
       <c r="E9">
-        <v>22736</v>
+        <v>1375</v>
       </c>
       <c r="F9">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>47341</v>
+      </c>
+      <c r="G9">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1150,19 +1180,22 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>968</v>
+        <v>2535</v>
       </c>
       <c r="D10">
-        <v>6157</v>
+        <v>17228</v>
       </c>
       <c r="E10">
-        <v>7125</v>
+        <v>307</v>
       </c>
       <c r="F10">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20070</v>
+      </c>
+      <c r="G10">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1170,19 +1203,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>2569</v>
+        <v>5855</v>
       </c>
       <c r="D11">
-        <v>12337</v>
+        <v>29452</v>
       </c>
       <c r="E11">
-        <v>14906</v>
+        <v>2215</v>
       </c>
       <c r="F11">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>37522</v>
+      </c>
+      <c r="G11">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1190,19 +1226,22 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>1667</v>
+        <v>5932</v>
       </c>
       <c r="D12">
-        <v>8056</v>
+        <v>30206</v>
       </c>
       <c r="E12">
-        <v>9723</v>
+        <v>1335</v>
       </c>
       <c r="F12">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>37473</v>
+      </c>
+      <c r="G12">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1210,19 +1249,22 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>2766</v>
+        <v>9694</v>
       </c>
       <c r="D13">
-        <v>11302</v>
+        <v>25431</v>
       </c>
       <c r="E13">
-        <v>14068</v>
+        <v>3923</v>
       </c>
       <c r="F13">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>39048</v>
+      </c>
+      <c r="G13">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1230,19 +1272,22 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>2070</v>
+        <v>5970</v>
       </c>
       <c r="D14">
-        <v>6546</v>
+        <v>23293</v>
       </c>
       <c r="E14">
-        <v>8616</v>
+        <v>460</v>
       </c>
       <c r="F14">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29723</v>
+      </c>
+      <c r="G14">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1250,19 +1295,22 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>1048</v>
+        <v>3107</v>
       </c>
       <c r="D15">
-        <v>7142</v>
+        <v>19589</v>
       </c>
       <c r="E15">
-        <v>8190</v>
+        <v>1271</v>
       </c>
       <c r="F15">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>23967</v>
+      </c>
+      <c r="G15">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -1270,19 +1318,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>140</v>
+        <v>3068</v>
       </c>
       <c r="D16">
-        <v>1193</v>
+        <v>6583</v>
       </c>
       <c r="E16">
-        <v>1333</v>
+        <v>493</v>
       </c>
       <c r="F16">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10144</v>
+      </c>
+      <c r="G16">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1290,19 +1341,22 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>477</v>
+        <v>2564</v>
       </c>
       <c r="D17">
-        <v>3318</v>
+        <v>18996</v>
       </c>
       <c r="E17">
-        <v>3795</v>
+        <v>324</v>
       </c>
       <c r="F17">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>21884</v>
+      </c>
+      <c r="G17">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1310,19 +1364,22 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>989</v>
+        <v>2826</v>
       </c>
       <c r="D18">
-        <v>3431</v>
+        <v>14361</v>
       </c>
       <c r="E18">
-        <v>4420</v>
+        <v>655</v>
       </c>
       <c r="F18">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>17842</v>
+      </c>
+      <c r="G18">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1330,19 +1387,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>3094</v>
+        <v>3766</v>
       </c>
       <c r="D19">
-        <v>9372</v>
+        <v>23666</v>
       </c>
       <c r="E19">
-        <v>12466</v>
+        <v>506</v>
       </c>
       <c r="F19">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>27938</v>
+      </c>
+      <c r="G19">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1350,19 +1410,22 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>2057</v>
+        <v>4561</v>
       </c>
       <c r="D20">
-        <v>8158</v>
+        <v>23460</v>
       </c>
       <c r="E20">
-        <v>10215</v>
+        <v>171</v>
       </c>
       <c r="F20">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>28192</v>
+      </c>
+      <c r="G20">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1370,19 +1433,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>1650</v>
+        <v>3599</v>
       </c>
       <c r="D21">
-        <v>3383</v>
+        <v>13232</v>
       </c>
       <c r="E21">
-        <v>5033</v>
+        <v>687</v>
       </c>
       <c r="F21">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>17518</v>
+      </c>
+      <c r="G21">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1390,19 +1456,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>375</v>
+        <v>1393</v>
       </c>
       <c r="D22">
-        <v>2061</v>
+        <v>7136</v>
       </c>
       <c r="E22">
-        <v>2436</v>
+        <v>282</v>
       </c>
       <c r="F22">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8811</v>
+      </c>
+      <c r="G22">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1410,19 +1479,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>176</v>
+        <v>591</v>
       </c>
       <c r="D23">
-        <v>2452</v>
+        <v>7432</v>
       </c>
       <c r="E23">
-        <v>2628</v>
+        <v>408</v>
       </c>
       <c r="F23">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8431</v>
+      </c>
+      <c r="G23">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1430,19 +1502,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>582</v>
+        <v>1722</v>
       </c>
       <c r="D24">
-        <v>4129</v>
+        <v>8692</v>
       </c>
       <c r="E24">
-        <v>4711</v>
+        <v>237</v>
       </c>
       <c r="F24">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10651</v>
+      </c>
+      <c r="G24">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1450,19 +1525,22 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>935</v>
+        <v>1368</v>
       </c>
       <c r="D25">
-        <v>10058</v>
+        <v>20247</v>
       </c>
       <c r="E25">
-        <v>10993</v>
+        <v>241</v>
       </c>
       <c r="F25">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>21856</v>
+      </c>
+      <c r="G25">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1470,19 +1548,22 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>852</v>
+        <v>969</v>
       </c>
       <c r="D26">
-        <v>3226</v>
+        <v>8854</v>
       </c>
       <c r="E26">
-        <v>4078</v>
+        <v>14</v>
       </c>
       <c r="F26">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9837</v>
+      </c>
+      <c r="G26">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1490,16 +1571,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>4890</v>
+        <v>8823</v>
       </c>
       <c r="D27">
-        <v>14794</v>
+        <v>27170</v>
       </c>
       <c r="E27">
-        <v>19684</v>
+        <v>1617</v>
       </c>
       <c r="F27">
-        <v>953</v>
+        <v>37610</v>
+      </c>
+      <c r="G27">
+        <v>1728</v>
       </c>
     </row>
   </sheetData>
